--- a/demo/demo_results.xlsx
+++ b/demo/demo_results.xlsx
@@ -170,7 +170,7 @@
         <v>46119</v>
       </c>
       <c r="E2" s="0">
-        <v>0.16705525804187887</v>
+        <v>0.34915658194942012</v>
       </c>
     </row>
     <row r="3">
@@ -187,7 +187,7 @@
         <v>46119</v>
       </c>
       <c r="E3" s="0">
-        <v>0.17034384774193551</v>
+        <v>0.37243783834898936</v>
       </c>
     </row>
     <row r="4">
@@ -204,7 +204,7 @@
         <v>46119</v>
       </c>
       <c r="E4" s="0">
-        <v>0.17284317591397849</v>
+        <v>0.390131593212662</v>
       </c>
     </row>
     <row r="5">
@@ -221,7 +221,7 @@
         <v>46119</v>
       </c>
       <c r="E5" s="0">
-        <v>0.17737203372948501</v>
+        <v>0.42219320916864012</v>
       </c>
     </row>
   </sheetData>
@@ -278,7 +278,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="0">
-        <v>0.16562707051499717</v>
+        <v>0.33904586488446437</v>
       </c>
     </row>
     <row r="3">
@@ -298,7 +298,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="0">
-        <v>0.17472237002829655</v>
+        <v>0.40343516829813009</v>
       </c>
     </row>
     <row r="4">
@@ -318,7 +318,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="0">
-        <v>0.17829283884550085</v>
+        <v>0.42871196096051956</v>
       </c>
     </row>
     <row r="5">
@@ -338,7 +338,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="0">
-        <v>0.18246464977928695</v>
+        <v>0.45824589765025881</v>
       </c>
     </row>
     <row r="6">
@@ -358,7 +358,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="0">
-        <v>0.1684834455687606</v>
+        <v>0.35926729901437587</v>
       </c>
     </row>
     <row r="7">
@@ -378,7 +378,7 @@
         <v>18</v>
       </c>
       <c r="F7" s="0">
-        <v>0.16596532545557444</v>
+        <v>0.34144050839984863</v>
       </c>
     </row>
     <row r="8">
@@ -398,7 +398,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="0">
-        <v>0.16739351298245614</v>
+        <v>0.3515512254648045</v>
       </c>
     </row>
     <row r="9">
@@ -418,7 +418,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="0">
-        <v>0.17227941767968308</v>
+        <v>0.38614052068702148</v>
       </c>
     </row>
   </sheetData>

--- a/demo/demo_results.xlsx
+++ b/demo/demo_results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="57" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="59" uniqueCount="24">
   <si>
     <t>hashcode</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>concentration</t>
+  </si>
+  <si>
+    <t>volume_for_cs_assay</t>
   </si>
   <si>
     <t>well_no</t>
@@ -129,7 +132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="true"/>
@@ -137,6 +140,7 @@
     <col min="3" max="3" width="6.85546875" customWidth="true"/>
     <col min="4" max="4" width="16.5703125" customWidth="true"/>
     <col min="5" max="5" width="13.42578125" customWidth="true"/>
+    <col min="6" max="6" width="19.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -155,6 +159,9 @@
       <c r="E1" s="0" t="s">
         <v>11</v>
       </c>
+      <c r="F1" s="0" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -170,7 +177,10 @@
         <v>46119</v>
       </c>
       <c r="E2" s="0">
-        <v>0.34915658194942012</v>
+        <v>10.474697458482604</v>
+      </c>
+      <c r="F2" s="0">
+        <v>305.14127839601787</v>
       </c>
     </row>
     <row r="3">
@@ -187,7 +197,10 @@
         <v>46119</v>
       </c>
       <c r="E3" s="0">
-        <v>0.37243783834898936</v>
+        <v>11.173135150469681</v>
+      </c>
+      <c r="F3" s="0">
+        <v>363.09165146831708</v>
       </c>
     </row>
     <row r="4">
@@ -204,7 +217,10 @@
         <v>46119</v>
       </c>
       <c r="E4" s="0">
-        <v>0.390131593212662</v>
+        <v>11.703947796379861</v>
+      </c>
+      <c r="F4" s="0">
+        <v>385.84076486446765</v>
       </c>
     </row>
     <row r="5">
@@ -221,7 +237,10 @@
         <v>46119</v>
       </c>
       <c r="E5" s="0">
-        <v>0.42219320916864012</v>
+        <v>12.665796275059204</v>
+      </c>
+      <c r="F5" s="0">
+        <v>412.42130788523286</v>
       </c>
     </row>
   </sheetData>
@@ -230,7 +249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="true"/>
@@ -239,6 +258,7 @@
     <col min="4" max="4" width="16.5703125" customWidth="true"/>
     <col min="5" max="5" width="8.28515625" customWidth="true"/>
     <col min="6" max="6" width="13.42578125" customWidth="true"/>
+    <col min="7" max="7" width="19.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -255,11 +275,14 @@
         <v>10</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F1" s="0" t="s">
         <v>11</v>
       </c>
+      <c r="G1" s="0" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -275,10 +298,13 @@
         <v>46119</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="0">
-        <v>0.33904586488446437</v>
+        <v>10.17137594653393</v>
+      </c>
+      <c r="G2" s="0">
+        <v>305.14127839601787</v>
       </c>
     </row>
     <row r="3">
@@ -295,10 +321,13 @@
         <v>46119</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="0">
-        <v>0.40343516829813009</v>
+        <v>12.103055048943903</v>
+      </c>
+      <c r="G3" s="0">
+        <v>363.09165146831708</v>
       </c>
     </row>
     <row r="4">
@@ -315,10 +344,13 @@
         <v>46119</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="0">
-        <v>0.42871196096051956</v>
+        <v>12.861358828815588</v>
+      </c>
+      <c r="G4" s="0">
+        <v>385.84076486446765</v>
       </c>
     </row>
     <row r="5">
@@ -335,10 +367,13 @@
         <v>46119</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="0">
-        <v>0.45824589765025881</v>
+        <v>13.747376929507762</v>
+      </c>
+      <c r="G5" s="0">
+        <v>412.42130788523286</v>
       </c>
     </row>
     <row r="6">
@@ -355,10 +390,13 @@
         <v>46119</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="0">
-        <v>0.35926729901437587</v>
+        <v>10.778018970431278</v>
+      </c>
+      <c r="G6" s="0">
+        <v>323.34056911293834</v>
       </c>
     </row>
     <row r="7">
@@ -375,10 +413,13 @@
         <v>46119</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="0">
-        <v>0.34144050839984863</v>
+        <v>10.24321525199546</v>
+      </c>
+      <c r="G7" s="0">
+        <v>307.29645755986382</v>
       </c>
     </row>
     <row r="8">
@@ -395,10 +436,13 @@
         <v>46119</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="0">
-        <v>0.3515512254648045</v>
+        <v>10.546536763944134</v>
+      </c>
+      <c r="G8" s="0">
+        <v>316.39610291832401</v>
       </c>
     </row>
     <row r="9">
@@ -415,10 +459,13 @@
         <v>46119</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="0">
-        <v>0.38614052068702148</v>
+        <v>11.584215620610646</v>
+      </c>
+      <c r="G9" s="0">
+        <v>347.52646861831937</v>
       </c>
     </row>
   </sheetData>
@@ -436,10 +483,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
